--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98770</v>
+        <v>98773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98773</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457319</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136458324</v>
       </c>
       <c r="B4" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136457356</v>
       </c>
       <c r="B5" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98779</v>
+        <v>98781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457319</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136458324</v>
       </c>
       <c r="B4" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136457356</v>
       </c>
       <c r="B5" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98781</v>
+        <v>98787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457319</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136458324</v>
       </c>
       <c r="B4" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136457356</v>
       </c>
       <c r="B5" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98787</v>
+        <v>98789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457319</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136458324</v>
       </c>
       <c r="B4" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136457356</v>
       </c>
       <c r="B5" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98789</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36050-2026 artfynd.xlsx
+++ b/artfynd/A 36050-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136458298</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136458129</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
